--- a/sigma_plots.xlsx
+++ b/sigma_plots.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635BC988-6539-40DC-937A-D3C6EC0F626B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE0515C-0736-4C5C-A759-B9BBA662C153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C750A67F-B026-43C6-AFE1-D1655638C626}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="22">
   <si>
     <t>Sigma 0.75</t>
   </si>
@@ -69,6 +69,39 @@
   </si>
   <si>
     <t>PM</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>([[9.95587988e-01, 9.99490867e-01, 9.98581866e-01, 3.06601232e-02,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        2.74636788e-02],</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       [9.98805243e-01, 9.99863114e-01, 9.99617955e-01, 7.53298804e-03,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        6.75059649e-03],</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       [9.99689875e-01, 9.99964425e-01, 9.99900722e-01, 2.26392374e-03,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        1.62239407e-03],</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       [9.99920969e-01, 9.99990891e-01, 9.99974637e-01, 3.08837253e-04,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        5.96775566e-04],</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       [9.99980015e-01, 9.99997689e-01, 9.99993573e-01, 3.88481574e-04,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        1.88616816e-04]])</t>
   </si>
 </sst>
 </file>
@@ -142,15 +175,15 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="60% - Accent1" xfId="1" builtinId="32"/>
@@ -468,172 +501,272 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81776ACB-23F6-4FE3-8674-6E7C26AF9720}">
-  <dimension ref="B1:K17"/>
+  <dimension ref="B1:L21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="C2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="4"/>
       <c r="J2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>0.32</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="1"/>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
       <c r="F3">
         <v>0.38</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="1"/>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
       <c r="J3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>0.46</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="1"/>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
       <c r="F4">
         <v>0.53</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="1"/>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
       <c r="J4" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>0.6</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
       <c r="F5">
         <v>0.68</v>
       </c>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G5" s="1"/>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1.7</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
       <c r="F6">
         <v>1.19333333</v>
       </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G6" s="2"/>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1.78</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
       <c r="F7">
         <v>1.26666667</v>
       </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
+      <c r="G7" s="2"/>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="F9" s="1" t="s">
+      <c r="C9" s="5"/>
+      <c r="F9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="F10" s="2" t="s">
+      <c r="C10" s="4"/>
+      <c r="F10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1E-3</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
       <c r="F11">
         <v>0.1</v>
       </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G11" s="3"/>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12">
-        <v>2.8E-3</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>2.3E-2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
       <c r="F12">
         <v>0.15</v>
       </c>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G12" s="3"/>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="C13" s="5"/>
+        <v>0.67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
       <c r="F13">
         <v>0.2</v>
       </c>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G13" s="3"/>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="C14" s="5"/>
+        <v>0.72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
       <c r="F14">
         <v>0.39</v>
       </c>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15">
-        <v>0.95</v>
-      </c>
-      <c r="C15" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
       <c r="F15">
         <v>0.42</v>
       </c>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <v>0.98</v>
-      </c>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <v>1.2</v>
-      </c>
-      <c r="C17" s="4"/>
+      <c r="G15" s="2"/>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
